--- a/output/stock_quant_scores/HIMS_income_df.xlsx
+++ b/output/stock_quant_scores/HIMS_income_df.xlsx
@@ -1185,7 +1185,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>-115042000</v>
+      </c>
       <c r="L6" t="n">
         <v>-10000</v>
       </c>
@@ -1199,10 +1201,14 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>-0.58</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-107659000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1226,9 +1232,13 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>204494000</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>271878000</v>
+      </c>
       <c r="AS6" t="inlineStr"/>
     </row>
   </sheetData>
